--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129259111</v>
       </c>
       <c r="B2" t="n">
-        <v>57646</v>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129259111</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129259111</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,117 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129259134</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tvyfallön, Skärså, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>613880</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6805766</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Söderlund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Söderlund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>129259134</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,6 +899,228 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129960495</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tvyfallön, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613890</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6805858</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129960537</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tvyfallön, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>613960</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6805869</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka plantor</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129960495</v>
+        <v>129960537</v>
       </c>
       <c r="B4" t="n">
         <v>98794</v>
@@ -929,16 +929,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613890</v>
+        <v>613960</v>
       </c>
       <c r="R4" t="n">
-        <v>6805858</v>
+        <v>6805869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>Enstaka plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960537</v>
+        <v>129960495</v>
       </c>
       <c r="B5" t="n">
         <v>98794</v>
@@ -1044,8 +1036,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613960</v>
+        <v>613890</v>
       </c>
       <c r="R5" t="n">
-        <v>6805869</v>
+        <v>6805858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129960537</v>
+        <v>129960495</v>
       </c>
       <c r="B4" t="n">
         <v>98794</v>
@@ -929,8 +929,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -940,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613960</v>
+        <v>613890</v>
       </c>
       <c r="R4" t="n">
-        <v>6805869</v>
+        <v>6805858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +988,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960495</v>
+        <v>129960537</v>
       </c>
       <c r="B5" t="n">
         <v>98794</v>
@@ -1036,16 +1044,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613890</v>
+        <v>613960</v>
       </c>
       <c r="R5" t="n">
-        <v>6805858</v>
+        <v>6805869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>Enstaka plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129259134</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129960495</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129960537</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129960495</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129960537</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129259134</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129960495</v>
+        <v>129960537</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,16 +929,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613890</v>
+        <v>613960</v>
       </c>
       <c r="R4" t="n">
-        <v>6805858</v>
+        <v>6805869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>Enstaka plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960537</v>
+        <v>129960495</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,8 +1036,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613960</v>
+        <v>613890</v>
       </c>
       <c r="R5" t="n">
-        <v>6805869</v>
+        <v>6805858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129960495</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129960537</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129259134</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129960495</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129960537</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129259111</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129259134</v>
+        <v>129259098</v>
       </c>
       <c r="B3" t="n">
-        <v>58113</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,24 +818,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tvyfallön, Skärså, Hls</t>
+          <t>Tvyfallön, Björnvågen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613880</v>
+        <v>614001</v>
       </c>
       <c r="R3" t="n">
-        <v>6805766</v>
+        <v>6805626</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,60 +905,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129960495</v>
+        <v>129259134</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tvyfallön, Hls</t>
+          <t>Tvyfallön, Skärså, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613890</v>
+        <v>613880</v>
       </c>
       <c r="R4" t="n">
-        <v>6805858</v>
+        <v>6805766</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,17 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,29 +998,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
+          <t>Tomas Söderlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
+          <t>Tomas Söderlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129960537</v>
+        <v>129960495</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,8 +1044,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1055,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613960</v>
+        <v>613890</v>
       </c>
       <c r="R5" t="n">
-        <v>6805869</v>
+        <v>6805858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1103,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1128,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129960537</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tvyfallön, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>613960</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6805869</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norrala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka plantor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31805-2024 artfynd.xlsx
+++ b/artfynd/A 31805-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129259134</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,8 +1260,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960537</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>